--- a/tame_output/ON/bt/strategyON_20240715.xlsx
+++ b/tame_output/ON/bt/strategyON_20240715.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>-66.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.6%</t>
+          <t>457.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-142.7%</t>
+          <t>-142.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-134.9%</t>
+          <t>-135.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-131.0%</t>
+          <t>-126.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-21.9%</t>
         </is>
       </c>
     </row>
@@ -47022,10 +47022,10 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.702116487456343</v>
+        <v>-2.737002324075296</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.37358109197028</v>
+        <v>1.359626757322699</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8054774053455968</v>
@@ -47045,10 +47045,10 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.654460756895287</v>
+        <v>-2.689346593514241</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.399025141222507</v>
+        <v>1.385070806574926</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8531331359066524</v>
@@ -47068,10 +47068,10 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.553942598396532</v>
+        <v>-2.588828435015486</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.444124777996734</v>
+        <v>1.430170443349152</v>
       </c>
       <c r="F1979" t="n">
         <v>0.953651294405407</v>
@@ -47091,10 +47091,10 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.614609188798922</v>
+        <v>-2.649495025417875</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.40661281431165</v>
+        <v>1.392658479664069</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8719529776868733</v>
@@ -47114,10 +47114,10 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.569770787190524</v>
+        <v>-2.604656623809477</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.428645877565638</v>
+        <v>1.414691542918057</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8764964106317428</v>
@@ -47137,10 +47137,10 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.670529422947522</v>
+        <v>-2.705415259566476</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.392503362893917</v>
+        <v>1.378549028246335</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7876708419047374</v>
@@ -47160,10 +47160,10 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.626326585861622</v>
+        <v>-2.661212422480575</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.416064100256114</v>
+        <v>1.402109765608533</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8318736789906378</v>
@@ -47183,10 +47183,10 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.663305613525065</v>
+        <v>-2.698191450144019</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.399682489659984</v>
+        <v>1.385728155012403</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8688475807819683</v>
@@ -47206,10 +47206,10 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.505014195985793</v>
+        <v>-2.539900032604746</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.514246821858733</v>
+        <v>1.500292487211151</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8688475807819683</v>
@@ -47229,10 +47229,10 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.297372192351316</v>
+        <v>-2.33225802897027</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.595744327906776</v>
+        <v>1.581789993259195</v>
       </c>
       <c r="F1986" t="n">
         <v>1.076489584416445</v>
@@ -47252,10 +47252,10 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.246340099628788</v>
+        <v>-2.281225936247742</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.611105393234058</v>
+        <v>1.597151058586476</v>
       </c>
       <c r="F1987" t="n">
         <v>1.127521677138973</v>
@@ -47275,10 +47275,10 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.181115918501582</v>
+        <v>-2.216001755120536</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.654382469777645</v>
+        <v>1.640428135130064</v>
       </c>
       <c r="F1988" t="n">
         <v>1.192745858266178</v>
@@ -47298,10 +47298,10 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.143688898430449</v>
+        <v>-2.178574735049402</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.665314250105379</v>
+        <v>1.651359915457797</v>
       </c>
       <c r="F1989" t="n">
         <v>1.19799739629536</v>
@@ -47321,10 +47321,10 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.163800554465157</v>
+        <v>-2.198686391084111</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.658526380022736</v>
+        <v>1.644572045375154</v>
       </c>
       <c r="F1990" t="n">
         <v>1.209024741292779</v>
@@ -47344,10 +47344,10 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.110055740037952</v>
+        <v>-2.144941576656906</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.840582076814828</v>
+        <v>1.826627742167247</v>
       </c>
       <c r="F1991" t="n">
         <v>1.219088050733241</v>
@@ -47367,10 +47367,10 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.03527347901294</v>
+        <v>-2.070159315631893</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.990607890442651</v>
+        <v>1.976653555795069</v>
       </c>
       <c r="F1992" t="n">
         <v>1.293870311758254</v>
@@ -47390,10 +47390,10 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.009189394749132</v>
+        <v>-2.044075231368085</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.992749500162033</v>
+        <v>1.978795165514451</v>
       </c>
       <c r="F1993" t="n">
         <v>1.293870311758254</v>
@@ -47413,10 +47413,10 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-1.931058213900185</v>
+        <v>-1.965944050519139</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.022195168085391</v>
+        <v>2.00824083343781</v>
       </c>
       <c r="F1994" t="n">
         <v>1.368047122641939</v>
@@ -47436,10 +47436,10 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.922165752506902</v>
+        <v>-1.957051589125856</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.043306558369496</v>
+        <v>2.029352223721914</v>
       </c>
       <c r="F1995" t="n">
         <v>1.368047122641939</v>
@@ -47459,10 +47459,10 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.09064186947678</v>
+        <v>-2.125527706095733</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.967771158986129</v>
+        <v>1.953816824338547</v>
       </c>
       <c r="F1996" t="n">
         <v>1.340099286925358</v>
@@ -47482,10 +47482,10 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.392842340615196</v>
+        <v>-1.42772817723415</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.228160667718623</v>
+        <v>2.214206333071042</v>
       </c>
       <c r="F1997" t="n">
         <v>1.269751227554947</v>
@@ -47505,10 +47505,10 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.370121236932044</v>
+        <v>-1.405007073550998</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.227913131688789</v>
+        <v>2.213958797041208</v>
       </c>
       <c r="F1998" t="n">
         <v>1.269751227554947</v>
@@ -47528,10 +47528,10 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.368396193642</v>
+        <v>-1.403282030260954</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.387509274855976</v>
+        <v>2.373554940208394</v>
       </c>
       <c r="F1999" t="n">
         <v>1.271476270844991</v>
@@ -47551,10 +47551,10 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.523177200420256</v>
+        <v>-1.558063037039209</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.36267469463832</v>
+        <v>2.348720359990739</v>
       </c>
       <c r="F2000" t="n">
         <v>1.238108596790515</v>
@@ -47574,10 +47574,10 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.516122510205082</v>
+        <v>-1.551008346824035</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.362171926713935</v>
+        <v>2.348217592066353</v>
       </c>
       <c r="F2001" t="n">
         <v>1.245163287005689</v>
@@ -47597,10 +47597,10 @@
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.489171285878594</v>
+        <v>-1.524057122497547</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.382958570089272</v>
+        <v>2.36900423544169</v>
       </c>
       <c r="F2002" t="n">
         <v>1.260043633033408</v>
@@ -47620,10 +47620,10 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.62512429393491</v>
+        <v>-1.660010130553863</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.512680499011705</v>
+        <v>2.498726164364124</v>
       </c>
       <c r="F2003" t="n">
         <v>1.260043633033408</v>
@@ -47643,10 +47643,10 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.647532411739782</v>
+        <v>-1.682418248358736</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.495833946792749</v>
+        <v>2.481879612145168</v>
       </c>
       <c r="F2004" t="n">
         <v>1.260043633033408</v>
@@ -47666,10 +47666,10 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.795538179219181</v>
+        <v>-1.830424015838135</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.438685639350627</v>
+        <v>2.424731304703045</v>
       </c>
       <c r="F2005" t="n">
         <v>1.173316624169866</v>
@@ -47689,10 +47689,10 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.804979105107711</v>
+        <v>-1.839864941726665</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.491162986717062</v>
+        <v>2.477208652069481</v>
       </c>
       <c r="F2006" t="n">
         <v>1.295743741713258</v>
@@ -47712,10 +47712,10 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.803692341568154</v>
+        <v>-1.838578178187108</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.494568786678186</v>
+        <v>2.480614452030604</v>
       </c>
       <c r="F2007" t="n">
         <v>1.297030505252814</v>
@@ -47735,10 +47735,10 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.805249395557446</v>
+        <v>-1.840135232176399</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.492057777976244</v>
+        <v>2.478103443328663</v>
       </c>
       <c r="F2008" t="n">
         <v>1.297030505252814</v>
@@ -47758,10 +47758,10 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.81252128108091</v>
+        <v>-1.847407117699864</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.483969253369721</v>
+        <v>2.470014918722139</v>
       </c>
       <c r="F2009" t="n">
         <v>1.28975861972935</v>
@@ -47781,10 +47781,10 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.810680262022659</v>
+        <v>-1.845566098641613</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.483139671203173</v>
+        <v>2.469185336555592</v>
       </c>
       <c r="F2010" t="n">
         <v>1.291026846400818</v>
@@ -47804,10 +47804,10 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.81758896752234</v>
+        <v>-1.852474804141293</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.49344959586922</v>
+        <v>2.479495261221639</v>
       </c>
       <c r="F2011" t="n">
         <v>1.291026846400818</v>
@@ -47827,10 +47827,10 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.819150610337199</v>
+        <v>-1.854036446956153</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.492824938743276</v>
+        <v>2.478870604095694</v>
       </c>
       <c r="F2012" t="n">
         <v>1.291026846400818</v>
@@ -47850,10 +47850,10 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.847051397446672</v>
+        <v>-1.881937234065626</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.480188665026489</v>
+        <v>2.466234330378907</v>
       </c>
       <c r="F2013" t="n">
         <v>1.256429922257883</v>
@@ -47873,10 +47873,10 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.850084394959346</v>
+        <v>-1.8849702315783</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.475739909998618</v>
+        <v>2.461785575351036</v>
       </c>
       <c r="F2014" t="n">
         <v>1.253396924745209</v>
@@ -47896,10 +47896,10 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.870145716235853</v>
+        <v>-1.905031552854807</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.534421341078519</v>
+        <v>2.520467006430938</v>
       </c>
       <c r="F2015" t="n">
         <v>1.233335603468702</v>
@@ -47919,10 +47919,10 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.126866534230677</v>
+        <v>-2.161752370849631</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.572044732882437</v>
+        <v>2.558090398234855</v>
       </c>
       <c r="F2016" t="n">
         <v>1.124921029324887</v>
@@ -47942,10 +47942,10 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.280852952006818</v>
+        <v>-2.315738788625771</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.57943043491762</v>
+        <v>2.565476100270039</v>
       </c>
       <c r="F2017" t="n">
         <v>1.124921029324887</v>
@@ -47965,10 +47965,10 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.230331048179152</v>
+        <v>-2.265216884798106</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.585690398568807</v>
+        <v>2.571736063921226</v>
       </c>
       <c r="F2018" t="n">
         <v>1.124921029324887</v>
@@ -47988,10 +47988,10 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.482806202186876</v>
+        <v>-2.51769203880583</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.496570826021132</v>
+        <v>2.48261649137355</v>
       </c>
       <c r="F2019" t="n">
         <v>1.124921029324887</v>
@@ -48011,10 +48011,10 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.752279004108584</v>
+        <v>-2.787164840727538</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.389992239771392</v>
+        <v>2.376037905123811</v>
       </c>
       <c r="F2020" t="n">
         <v>1.124921029324887</v>
@@ -48034,10 +48034,10 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.909823075838025</v>
+        <v>-2.944708912456979</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.331096353306937</v>
+        <v>2.317142018659355</v>
       </c>
       <c r="F2021" t="n">
         <v>1.058019224184613</v>
@@ -48057,10 +48057,10 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.038673626540072</v>
+        <v>-3.073559463159026</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.274633985762308</v>
+        <v>2.260679651114726</v>
       </c>
       <c r="F2022" t="n">
         <v>1.017025815333891</v>
@@ -48080,10 +48080,10 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.155641319178963</v>
+        <v>-3.190527155797917</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.390050965405796</v>
+        <v>2.376096630758214</v>
       </c>
       <c r="F2023" t="n">
         <v>1.017025815333891</v>
@@ -48103,10 +48103,10 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.240359261399917</v>
+        <v>-3.27524509801887</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.351010426481228</v>
+        <v>2.337056091833647</v>
       </c>
       <c r="F2024" t="n">
         <v>0.931909786405845</v>
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.848598253500581</v>
+        <v>3.735901217068432</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.304161172875873</v>
+        <v>-3.303904658161786</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.335719079459337</v>
+        <v>2.335821685344972</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.9303787681266608</v>
+        <v>0.9724153948312498</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.21596723379943</v>
+        <v>4.241189209822183</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240715.xlsx
+++ b/tame_output/ON/bt/strategyON_20240715.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-71.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.6%</t>
+          <t>121.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.4%</t>
+          <t>-66.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-492.0%</t>
+          <t>-497.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-142.6%</t>
+          <t>-144.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.0%</t>
+          <t>-135.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-126.8%</t>
+          <t>-131.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>75.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-24.9%</t>
         </is>
       </c>
     </row>
@@ -48126,16 +48126,16 @@
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.303904658161786</v>
+        <v>-3.357179916287754</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.335821685344972</v>
+        <v>2.314511582094585</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.9724153948312498</v>
+        <v>0.9219750408187648</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.241189209822183</v>
+        <v>4.210924997414693</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240715.xlsx
+++ b/tame_output/ON/bt/strategyON_20240715.xlsx
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647104</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.652163313301343</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215469</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69655362845669</v>
+        <v>3.696553628456692</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.735901217068432</v>
+        <v>3.735901217068434</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>

--- a/tame_output/ON/bt/strategyON_20240715.xlsx
+++ b/tame_output/ON/bt/strategyON_20240715.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>49.6%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.7%</t>
+          <t>121.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.7%</t>
+          <t>-66.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.5%</t>
+          <t>457.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-85.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2025"/>
+  <dimension ref="A1:G2026"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.735901217068434</v>
+        <v>3.750058176253288</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
@@ -48136,6 +48136,29 @@
       </c>
       <c r="G2025" t="n">
         <v>4.210924997414693</v>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" s="2" t="n">
+        <v>45488</v>
+      </c>
+      <c r="B2026" t="n">
+        <v>3.736620209407807</v>
+      </c>
+      <c r="C2026" t="n">
+        <v>3.61225762849205</v>
+      </c>
+      <c r="D2026" t="n">
+        <v>-3.357179916287754</v>
+      </c>
+      <c r="E2026" t="n">
+        <v>2.314511582094585</v>
+      </c>
+      <c r="F2026" t="n">
+        <v>0.9219750408187648</v>
+      </c>
+      <c r="G2026" t="n">
+        <v>3.605321425478418</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240715.xlsx
+++ b/tame_output/ON/bt/strategyON_20240715.xlsx
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994894</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637086</v>
+        <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301343</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215469</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456692</v>
+        <v>3.69655362845669</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253288</v>
+        <v>3.750058176253286</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.736620209407807</v>
+        <v>3.736620209407805</v>
       </c>
       <c r="C2026" t="n">
         <v>3.61225762849205</v>

--- a/tame_output/ON/bt/strategyON_20240715.xlsx
+++ b/tame_output/ON/bt/strategyON_20240715.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>44.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>48.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.7%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>-67.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.4%</t>
+          <t>457.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-497.3%</t>
+          <t>-505.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-144.8%</t>
+          <t>-148.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.3%</t>
+          <t>-135.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-131.8%</t>
+          <t>-139.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-85.5%</t>
+          <t>-86.6%</t>
         </is>
       </c>
     </row>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.838578178187108</v>
+        <v>-1.919402726995227</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.480614452030604</v>
+        <v>2.448284632507357</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.297030505252814</v>
+        <v>1.216205956444696</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.994620450770883</v>
+        <v>3.946125721486013</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.840135232176399</v>
+        <v>-1.920959780984518</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.478103443328663</v>
+        <v>2.445773623805415</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.297030505252814</v>
+        <v>1.216205956444696</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.992732263664658</v>
+        <v>3.944237534379788</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.847407117699864</v>
+        <v>-1.928231666507983</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.470014918722139</v>
+        <v>2.437685099198892</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.28975861972935</v>
+        <v>1.208934070921231</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.983189361953442</v>
+        <v>3.934694632668571</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.845566098641613</v>
+        <v>-1.926390647449731</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.469185336555592</v>
+        <v>2.436855517032344</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.291026846400818</v>
+        <v>1.2102022975927</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.982384308166475</v>
+        <v>3.933889578881605</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647104</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.852474804141293</v>
+        <v>-1.933299352949412</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.479495261221639</v>
+        <v>2.447165441698391</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.291026846400818</v>
+        <v>1.2102022975927</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.995457715032394</v>
+        <v>3.946962985747523</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.854036446956153</v>
+        <v>-1.934860995764272</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.478870604095694</v>
+        <v>2.446540784572447</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.291026846400818</v>
+        <v>1.2102022975927</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.995457715032394</v>
+        <v>3.946962985747523</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.881937234065626</v>
+        <v>-1.962761782873744</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.466234330378907</v>
+        <v>2.43390451085566</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.256429922257883</v>
+        <v>1.175605373449765</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.973223601673635</v>
+        <v>3.924728872388764</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.8849702315783</v>
+        <v>-1.965794780386418</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.461785575351036</v>
+        <v>2.429455755827789</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.253396924745209</v>
+        <v>1.172572375937091</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.96816824714323</v>
+        <v>3.919673517858358</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.905031552854807</v>
+        <v>-1.985856101662925</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.520467006430938</v>
+        <v>2.48813718690769</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.233335603468702</v>
+        <v>1.152511054660584</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.022837413967829</v>
+        <v>3.974342684682958</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.161752370849631</v>
+        <v>-2.24257691965775</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.558090398234855</v>
+        <v>2.525760578711608</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.124921029324887</v>
+        <v>1.044096480516769</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.098100388483387</v>
+        <v>4.049605659198516</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.315738788625771</v>
+        <v>-2.39656333743389</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.565476100270039</v>
+        <v>2.533146280746791</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.124921029324887</v>
+        <v>1.044096480516769</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.167080657629027</v>
+        <v>4.118585928344157</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.265216884798106</v>
+        <v>-2.346041433606224</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.571736063921226</v>
+        <v>2.539406244397978</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.124921029324887</v>
+        <v>1.044096480516769</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.153131859749148</v>
+        <v>4.104637130464277</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.51769203880583</v>
+        <v>-2.598516587613949</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.48261649137355</v>
+        <v>2.450286671850303</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.124921029324887</v>
+        <v>1.044096480516769</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.165002348804562</v>
+        <v>4.116507619519691</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.787164840727538</v>
+        <v>-2.867989389535657</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.376037905123811</v>
+        <v>2.343708085600563</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.124921029324887</v>
+        <v>1.044096480516769</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.166212883323506</v>
+        <v>4.117718154038634</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-2.944708912456979</v>
+        <v>-3.025533461265098</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.317142018659355</v>
+        <v>2.284812199136108</v>
       </c>
       <c r="F2021" t="n">
-        <v>1.058019224184613</v>
+        <v>0.9771946753764946</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.130193542466662</v>
+        <v>4.081698813181792</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.073559463159026</v>
+        <v>-3.154384011967144</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.260679651114726</v>
+        <v>2.228349831591479</v>
       </c>
       <c r="F2022" t="n">
-        <v>1.017025815333891</v>
+        <v>0.9362012665257731</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.100675349892419</v>
+        <v>4.052180620607547</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.190527155797917</v>
+        <v>-3.271351704606035</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.376096630758214</v>
+        <v>2.343766811234967</v>
       </c>
       <c r="F2023" t="n">
-        <v>1.017025815333891</v>
+        <v>0.9362012665257731</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.262879406591463</v>
+        <v>4.214384677306592</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.27524509801887</v>
+        <v>-3.356069646826989</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.337056091833647</v>
+        <v>2.304726272310399</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.931909786405845</v>
+        <v>0.8510852375977267</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.20665642719845</v>
+        <v>4.158161697913578</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.357179916287754</v>
+        <v>-3.438004465095873</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.314511582094585</v>
+        <v>2.282181762571337</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.9219750408187648</v>
+        <v>0.8411504920106465</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.210924997414693</v>
+        <v>4.162430268129821</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.736620209407805</v>
+        <v>3.721599267754082</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.61225762849205</v>
+        <v>3.60123802330538</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.357179916287754</v>
+        <v>-3.438004465095873</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.314511582094585</v>
+        <v>2.282181762571337</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.9219750408187648</v>
+        <v>0.8411504920106465</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.605321425478418</v>
+        <v>3.594301820291748</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240715.xlsx
+++ b/tame_output/ON/bt/strategyON_20240715.xlsx
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.2%</t>
+          <t>-66.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.3%</t>
+          <t>457.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-505.4%</t>
+          <t>-490.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-148.0%</t>
+          <t>-141.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.9%</t>
+          <t>-135.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-139.9%</t>
+          <t>-137.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-86.6%</t>
+          <t>-27.3%</t>
         </is>
       </c>
     </row>
@@ -47022,10 +47022,10 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.737002324075296</v>
+        <v>-2.702116487456343</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.359626757322699</v>
+        <v>1.37358109197028</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8054774053455968</v>
@@ -47045,10 +47045,10 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.689346593514241</v>
+        <v>-2.654460756895287</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.385070806574926</v>
+        <v>1.399025141222507</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8531331359066524</v>
@@ -47068,10 +47068,10 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.588828435015486</v>
+        <v>-2.553942598396532</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.430170443349152</v>
+        <v>1.444124777996734</v>
       </c>
       <c r="F1979" t="n">
         <v>0.953651294405407</v>
@@ -47091,10 +47091,10 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.649495025417875</v>
+        <v>-2.614609188798922</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.392658479664069</v>
+        <v>1.40661281431165</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8719529776868733</v>
@@ -47114,10 +47114,10 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.604656623809477</v>
+        <v>-2.569770787190524</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.414691542918057</v>
+        <v>1.428645877565638</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8764964106317428</v>
@@ -47137,10 +47137,10 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.705415259566476</v>
+        <v>-2.670529422947522</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.378549028246335</v>
+        <v>1.392503362893917</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7876708419047374</v>
@@ -47160,10 +47160,10 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.661212422480575</v>
+        <v>-2.626326585861622</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.402109765608533</v>
+        <v>1.416064100256114</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8318736789906378</v>
@@ -47183,10 +47183,10 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.698191450144019</v>
+        <v>-2.663305613525065</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.385728155012403</v>
+        <v>1.399682489659984</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8688475807819683</v>
@@ -47206,10 +47206,10 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.539900032604746</v>
+        <v>-2.505014195985793</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.500292487211151</v>
+        <v>1.514246821858733</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8688475807819683</v>
@@ -47229,10 +47229,10 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.33225802897027</v>
+        <v>-2.297372192351316</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.581789993259195</v>
+        <v>1.595744327906776</v>
       </c>
       <c r="F1986" t="n">
         <v>1.076489584416445</v>
@@ -47252,10 +47252,10 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.281225936247742</v>
+        <v>-2.246340099628788</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.597151058586476</v>
+        <v>1.611105393234058</v>
       </c>
       <c r="F1987" t="n">
         <v>1.127521677138973</v>
@@ -47275,10 +47275,10 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.216001755120536</v>
+        <v>-2.181115918501582</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.640428135130064</v>
+        <v>1.654382469777645</v>
       </c>
       <c r="F1988" t="n">
         <v>1.192745858266178</v>
@@ -47298,10 +47298,10 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.178574735049402</v>
+        <v>-2.143688898430449</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.651359915457797</v>
+        <v>1.665314250105379</v>
       </c>
       <c r="F1989" t="n">
         <v>1.19799739629536</v>
@@ -47321,10 +47321,10 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.198686391084111</v>
+        <v>-2.163800554465157</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.644572045375154</v>
+        <v>1.658526380022736</v>
       </c>
       <c r="F1990" t="n">
         <v>1.209024741292779</v>
@@ -47344,10 +47344,10 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.144941576656906</v>
+        <v>-2.110055740037952</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.826627742167247</v>
+        <v>1.840582076814828</v>
       </c>
       <c r="F1991" t="n">
         <v>1.219088050733241</v>
@@ -47367,10 +47367,10 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.070159315631893</v>
+        <v>-2.03527347901294</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.976653555795069</v>
+        <v>1.990607890442651</v>
       </c>
       <c r="F1992" t="n">
         <v>1.293870311758254</v>
@@ -47390,10 +47390,10 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.044075231368085</v>
+        <v>-2.009189394749132</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.978795165514451</v>
+        <v>1.992749500162033</v>
       </c>
       <c r="F1993" t="n">
         <v>1.293870311758254</v>
@@ -47413,10 +47413,10 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-1.965944050519139</v>
+        <v>-1.931058213900185</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.00824083343781</v>
+        <v>2.022195168085391</v>
       </c>
       <c r="F1994" t="n">
         <v>1.368047122641939</v>
@@ -47436,10 +47436,10 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.957051589125856</v>
+        <v>-1.922165752506902</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.029352223721914</v>
+        <v>2.043306558369496</v>
       </c>
       <c r="F1995" t="n">
         <v>1.368047122641939</v>
@@ -47459,10 +47459,10 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.125527706095733</v>
+        <v>-2.09064186947678</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.953816824338547</v>
+        <v>1.967771158986129</v>
       </c>
       <c r="F1996" t="n">
         <v>1.340099286925358</v>
@@ -47482,10 +47482,10 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.42772817723415</v>
+        <v>-1.392842340615196</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.214206333071042</v>
+        <v>2.228160667718623</v>
       </c>
       <c r="F1997" t="n">
         <v>1.269751227554947</v>
@@ -47505,10 +47505,10 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.405007073550998</v>
+        <v>-1.370121236932044</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.213958797041208</v>
+        <v>2.227913131688789</v>
       </c>
       <c r="F1998" t="n">
         <v>1.269751227554947</v>
@@ -47528,10 +47528,10 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.403282030260954</v>
+        <v>-1.368396193642</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.373554940208394</v>
+        <v>2.387509274855976</v>
       </c>
       <c r="F1999" t="n">
         <v>1.271476270844991</v>
@@ -47551,10 +47551,10 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.558063037039209</v>
+        <v>-1.523177200420256</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.348720359990739</v>
+        <v>2.36267469463832</v>
       </c>
       <c r="F2000" t="n">
         <v>1.238108596790515</v>
@@ -47574,10 +47574,10 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.551008346824035</v>
+        <v>-1.516122510205082</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.348217592066353</v>
+        <v>2.362171926713935</v>
       </c>
       <c r="F2001" t="n">
         <v>1.245163287005689</v>
@@ -47597,10 +47597,10 @@
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.524057122497547</v>
+        <v>-1.489171285878594</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.36900423544169</v>
+        <v>2.382958570089272</v>
       </c>
       <c r="F2002" t="n">
         <v>1.260043633033408</v>
@@ -47620,10 +47620,10 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.660010130553863</v>
+        <v>-1.62512429393491</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.498726164364124</v>
+        <v>2.512680499011705</v>
       </c>
       <c r="F2003" t="n">
         <v>1.260043633033408</v>
@@ -47643,10 +47643,10 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.682418248358736</v>
+        <v>-1.647532411739782</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.481879612145168</v>
+        <v>2.495833946792749</v>
       </c>
       <c r="F2004" t="n">
         <v>1.260043633033408</v>
@@ -47666,10 +47666,10 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.830424015838135</v>
+        <v>-1.795538179219181</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.424731304703045</v>
+        <v>2.438685639350627</v>
       </c>
       <c r="F2005" t="n">
         <v>1.173316624169866</v>
@@ -47689,10 +47689,10 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.839864941726665</v>
+        <v>-1.804979105107711</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.477208652069481</v>
+        <v>2.491162986717062</v>
       </c>
       <c r="F2006" t="n">
         <v>1.295743741713258</v>
@@ -47712,16 +47712,16 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.919402726995227</v>
+        <v>-1.857252712443352</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.448284632507357</v>
+        <v>2.473144638328106</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.216205956444696</v>
+        <v>1.243470134377616</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.946125721486013</v>
+        <v>3.962484228245764</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.920959780984518</v>
+        <v>-1.858809766432644</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.445773623805415</v>
+        <v>2.470633629626165</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.216205956444696</v>
+        <v>1.243470134377616</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.944237534379788</v>
+        <v>3.96059604113954</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.928231666507983</v>
+        <v>-1.866081651956108</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.437685099198892</v>
+        <v>2.462545105019641</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.208934070921231</v>
+        <v>1.236198248854152</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.934694632668571</v>
+        <v>3.951053139428323</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.926390647449731</v>
+        <v>-1.864240632897857</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.436855517032344</v>
+        <v>2.461715522853094</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.2102022975927</v>
+        <v>1.23746647552562</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.933889578881605</v>
+        <v>3.950248085641356</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.933299352949412</v>
+        <v>-1.871149338397537</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.447165441698391</v>
+        <v>2.472025447519141</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.2102022975927</v>
+        <v>1.23746647552562</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.946962985747523</v>
+        <v>3.963321492507276</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.934860995764272</v>
+        <v>-1.872710981212397</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.446540784572447</v>
+        <v>2.471400790393197</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.2102022975927</v>
+        <v>1.23746647552562</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.946962985747523</v>
+        <v>3.963321492507276</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.962761782873744</v>
+        <v>-1.90061176832187</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.43390451085566</v>
+        <v>2.45876451667641</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.175605373449765</v>
+        <v>1.202869551382685</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.924728872388764</v>
+        <v>3.941087379148517</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.965794780386418</v>
+        <v>-1.903644765834544</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.429455755827789</v>
+        <v>2.454315761648539</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.172572375937091</v>
+        <v>1.199836553870012</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.919673517858358</v>
+        <v>3.936032024618111</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.985856101662925</v>
+        <v>-1.923706087111051</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.48813718690769</v>
+        <v>2.51299719272844</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.152511054660584</v>
+        <v>1.179775232593504</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.974342684682958</v>
+        <v>3.99070119144271</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.24257691965775</v>
+        <v>-2.180426905105875</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.525760578711608</v>
+        <v>2.550620584532357</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.044096480516769</v>
+        <v>1.07136065844969</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.049605659198516</v>
+        <v>4.065964165958269</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.39656333743389</v>
+        <v>-2.334413322882016</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.533146280746791</v>
+        <v>2.558006286567541</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.044096480516769</v>
+        <v>1.07136065844969</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.118585928344157</v>
+        <v>4.134944435103908</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.346041433606224</v>
+        <v>-2.28389141905435</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.539406244397978</v>
+        <v>2.564266250218728</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.044096480516769</v>
+        <v>1.07136065844969</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.104637130464277</v>
+        <v>4.12099563722403</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.598516587613949</v>
+        <v>-2.536366573062074</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.450286671850303</v>
+        <v>2.475146677671052</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.044096480516769</v>
+        <v>1.07136065844969</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.116507619519691</v>
+        <v>4.132866126279444</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.867989389535657</v>
+        <v>-2.805839374983782</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.343708085600563</v>
+        <v>2.368568091421313</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.044096480516769</v>
+        <v>1.07136065844969</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.117718154038634</v>
+        <v>4.134076660798387</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.025533461265098</v>
+        <v>-2.963383446713224</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.284812199136108</v>
+        <v>2.309672204956858</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.9771946753764946</v>
+        <v>1.004458853309415</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.081698813181792</v>
+        <v>4.098057319941544</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.154384011967144</v>
+        <v>-3.09223399741527</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.228349831591479</v>
+        <v>2.253209837412228</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.9362012665257731</v>
+        <v>0.9634654444586936</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.052180620607547</v>
+        <v>4.0685391273673</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.271351704606035</v>
+        <v>-3.209201690054161</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.343766811234967</v>
+        <v>2.368626817055716</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.9362012665257731</v>
+        <v>0.9634654444586936</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.214384677306592</v>
+        <v>4.230743184066345</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.356069646826989</v>
+        <v>-3.293919632275115</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.304726272310399</v>
+        <v>2.329586278131149</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.8510852375977267</v>
+        <v>0.8783494155306473</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.158161697913578</v>
+        <v>4.174520204673331</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.438004465095873</v>
+        <v>-3.375854450543998</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.282181762571337</v>
+        <v>2.307041768392087</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.8411504920106465</v>
+        <v>0.8684146699435671</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.162430268129821</v>
+        <v>4.178788774889574</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.721599267754082</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.60123802330538</v>
+        <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.438004465095873</v>
+        <v>-3.28977123129661</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.282181762571337</v>
+        <v>2.350400694546944</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.8411504920106465</v>
+        <v>0.8684146699435671</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.594301820291748</v>
+        <v>4.187714413345476</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240715.xlsx
+++ b/tame_output/ON/bt/strategyON_20240715.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-490.5%</t>
+          <t>-490.6%</t>
         </is>
       </c>
     </row>
@@ -48149,10 +48149,10 @@
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.28977123129661</v>
+        <v>-3.290308592062268</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.350400694546944</v>
+        <v>2.350185750240681</v>
       </c>
       <c r="F2026" t="n">
         <v>0.8684146699435671</v>
